--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101442</v>
+        <v>101445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101445</v>
+        <v>101446</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536475</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98275</v>
+        <v>98280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101446</v>
+        <v>101451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98280</v>
+        <v>98282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99167</v>
+        <v>99168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536475</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2022 artfynd.xlsx
+++ b/artfynd/A 22629-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136536475</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136536938</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136536940</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136536941</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136536943</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136536947</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136536949</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136536527</v>
       </c>
       <c r="B9" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136537030</v>
       </c>
       <c r="B10" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136536776</v>
       </c>
       <c r="B11" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136536835</v>
       </c>
       <c r="B12" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136536737</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136536761</v>
       </c>
       <c r="B14" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
